--- a/echo_dataset_annotations.xlsx
+++ b/echo_dataset_annotations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="119">
   <si>
     <t>Filename</t>
   </si>
@@ -22,37 +22,154 @@
     <t>MRN</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Study Date</t>
+  </si>
+  <si>
+    <t>Overall_Diagnosis</t>
+  </si>
+  <si>
     <t>Label</t>
   </si>
   <si>
     <t>Disease_Type</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Study Date</t>
+    <t>Flag_Normal</t>
+  </si>
+  <si>
+    <t>Flag_HFrEF</t>
+  </si>
+  <si>
+    <t>Flag_RWMA</t>
+  </si>
+  <si>
+    <t>Flag_DCM</t>
+  </si>
+  <si>
+    <t>Flag_RV_Dysfunction</t>
+  </si>
+  <si>
+    <t>Flag_Diastolic_Dysfunction</t>
+  </si>
+  <si>
+    <t>Flag_LVH</t>
+  </si>
+  <si>
+    <t>Flag_HCM</t>
+  </si>
+  <si>
+    <t>Flag_Valvular_Disease</t>
+  </si>
+  <si>
+    <t>Flag_Elevated_PASP</t>
+  </si>
+  <si>
+    <t>Flag_Structural_Abnormality</t>
+  </si>
+  <si>
+    <t>Group_LV_Status</t>
+  </si>
+  <si>
+    <t>Group_Diastolic_Status</t>
+  </si>
+  <si>
+    <t>Group_RV_Status</t>
+  </si>
+  <si>
+    <t>Group_Atria_Status</t>
+  </si>
+  <si>
+    <t>Group_Valves_Status</t>
+  </si>
+  <si>
+    <t>Group_PASP_Status</t>
+  </si>
+  <si>
+    <t>Group_Structural_Status</t>
   </si>
   <si>
     <t>LVEF</t>
   </si>
   <si>
+    <t>LVEDVi</t>
+  </si>
+  <si>
+    <t>IVSd</t>
+  </si>
+  <si>
+    <t>PASP</t>
+  </si>
+  <si>
+    <t>E/A Ratio</t>
+  </si>
+  <si>
+    <t>LAVi</t>
+  </si>
+  <si>
+    <t>TAPSE</t>
+  </si>
+  <si>
+    <t>Impression</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
     <t>LVIDD</t>
   </si>
   <si>
     <t>LVIDS</t>
   </si>
   <si>
-    <t>IVSd</t>
+    <t>LVESVi</t>
   </si>
   <si>
     <t>LVPWd</t>
   </si>
   <si>
-    <t>PASP</t>
+    <t>Diastolic Dysfunction Grade</t>
+  </si>
+  <si>
+    <t>E Velocity</t>
+  </si>
+  <si>
+    <t>DecT</t>
+  </si>
+  <si>
+    <t>e' Medial</t>
+  </si>
+  <si>
+    <t>e' Lateral</t>
+  </si>
+  <si>
+    <t>E/e' Average</t>
+  </si>
+  <si>
+    <t>TV S'</t>
+  </si>
+  <si>
+    <t>RV PLAX</t>
+  </si>
+  <si>
+    <t>RAVi</t>
+  </si>
+  <si>
+    <t>LAd</t>
+  </si>
+  <si>
+    <t>TR Vmax</t>
+  </si>
+  <si>
+    <t>AV Vmax</t>
+  </si>
+  <si>
+    <t>AV Mean PG</t>
   </si>
   <si>
     <t>BP Systolic</t>
@@ -61,12 +178,6 @@
     <t>BP Diastolic</t>
   </si>
   <si>
-    <t>Diastolic Dysfunction Grade</t>
-  </si>
-  <si>
-    <t>E/A Ratio</t>
-  </si>
-  <si>
     <t>Mitral Regurgitation</t>
   </si>
   <si>
@@ -76,10 +187,7 @@
     <t>Tricuspid Regurgitation</t>
   </si>
   <si>
-    <t>Impression</t>
-  </si>
-  <si>
-    <t>Error</t>
+    <t>Pulmonary Regurgitation</t>
   </si>
   <si>
     <t>doc (7).pdf</t>
@@ -94,22 +202,46 @@
     <t>HUiTM0041482</t>
   </si>
   <si>
-    <t>RWMA</t>
+    <t>47</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>2024-01-03</t>
+  </si>
+  <si>
+    <t>2024-02-15</t>
+  </si>
+  <si>
+    <t>Abnormal</t>
+  </si>
+  <si>
+    <t>HFrEF</t>
+  </si>
+  <si>
+    <t>Diastolic Dysfunction</t>
+  </si>
+  <si>
+    <t>Abnormal (Reduced EF)</t>
   </si>
   <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>2024-01-03</t>
-  </si>
-  <si>
-    <t>2024-02-15</t>
+    <t>Abnormal (Grade 3)</t>
+  </si>
+  <si>
+    <t>Abnormal (Impression)</t>
+  </si>
+  <si>
+    <t>Abnormal (MR, AR, TR)</t>
+  </si>
+  <si>
+    <t>Abnormal (55 mmHg)</t>
+  </si>
+  <si>
+    <t>Abnormal (Effusion)</t>
   </si>
   <si>
     <t>46</t>
@@ -118,64 +250,31 @@
     <t>54</t>
   </si>
   <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>3.9</t>
+    <t>57</t>
   </si>
   <si>
     <t>1.0</t>
   </si>
   <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
     <t>0.8</t>
   </si>
   <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2.9</t>
-  </si>
-  <si>
-    <t>Minimal MR</t>
-  </si>
-  <si>
-    <t>Mild MR</t>
-  </si>
-  <si>
-    <t>Trivial AR</t>
-  </si>
-  <si>
-    <t>Mild AR</t>
-  </si>
-  <si>
-    <t>Minimal TR</t>
-  </si>
-  <si>
-    <t>Mild to moderate TR</t>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2.2</t>
   </si>
   <si>
     <t>1. Normal left ventricular size with mildly impaired systolic function, LVEF is 46%.
@@ -191,6 +290,96 @@
 4. Normal left atrial size, right ventricular size and right atrial size. No LVH or RVH
 5. Estimated PASP is least 55mmHg, assuming RAP is 3mmHg
 6. No significant valvular abnormality seen</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>2.48</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Minimal MR</t>
+  </si>
+  <si>
+    <t>Mild MR</t>
+  </si>
+  <si>
+    <t>Trivial AR</t>
+  </si>
+  <si>
+    <t>Mild AR</t>
+  </si>
+  <si>
+    <t>Minimal TR</t>
+  </si>
+  <si>
+    <t>Mild to moderate TR</t>
+  </si>
+  <si>
+    <t>Trivial PR</t>
   </si>
 </sst>
 </file>
@@ -548,10 +737,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:BF3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:58">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,126 +807,414 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:58">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S2" t="s">
-        <v>50</v>
+        <v>67</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U2" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="V2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" t="s">
+        <v>72</v>
+      </c>
+      <c r="X2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>63</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:58">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
+        <v>66</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S3" t="s">
-        <v>51</v>
+        <v>68</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="U3" t="s">
-        <v>55</v>
+        <v>72</v>
+      </c>
+      <c r="V3" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>109</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>111</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
